--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484054_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484054_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2674</v>
+        <v>7.6038</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5739</v>
+        <v>5.1067</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6935</v>
+        <v>2.4971</v>
       </c>
       <c r="G2" t="n">
         <v>5.783</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2941</v>
+        <v>0.6306</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2323</v>
+        <v>0.3005</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5264</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1989</v>
+        <v>7.548</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3685</v>
+        <v>7.4931</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1696</v>
+        <v>0.0548</v>
       </c>
       <c r="G3" t="n">
         <v>3.6845</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.161</v>
+        <v>0.5101</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6973</v>
+        <v>0.822</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5363</v>
+        <v>-0.3119</v>
       </c>
       <c r="V3" t="n">
         <v>3.3534</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9173</v>
+        <v>6.8135</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3377</v>
+        <v>7.6267</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4204</v>
+        <v>-0.8132</v>
       </c>
       <c r="G4" t="n">
         <v>4.8742</v>
@@ -766,13 +766,13 @@
         <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0078</v>
+        <v>0.904</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5726</v>
+        <v>0.8617</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4351</v>
+        <v>0.0424</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5437</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1781</v>
+        <v>1.2777</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2139</v>
+        <v>1.3976</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0358</v>
+        <v>-0.12</v>
       </c>
       <c r="G5" t="n">
         <v>1.4354</v>
@@ -844,13 +844,13 @@
         <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0718</v>
+        <v>0.1714</v>
       </c>
       <c r="T5" t="n">
-        <v>0.924</v>
+        <v>0.1077</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1479</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4484</v>
+        <v>0.34</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.289</v>
+        <v>-1.1449</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7374</v>
+        <v>1.4849</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6226</v>
@@ -922,13 +922,13 @@
         <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7418</v>
+        <v>0.6334</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4285</v>
+        <v>0.5726</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3133</v>
+        <v>0.0608</v>
       </c>
       <c r="V6" t="n">
         <v>-0.266</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.105</v>
+        <v>0.2592</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0307</v>
+        <v>1.2971</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9257</v>
+        <v>-1.038</v>
       </c>
       <c r="G7" t="n">
         <v>0.1345</v>
@@ -1000,13 +1000,13 @@
         <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5056</v>
+        <v>-0.3514</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4364</v>
+        <v>-0.17</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0692</v>
+        <v>-0.1814</v>
       </c>
       <c r="V7" t="n">
         <v>0.6745</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9522</v>
+        <v>-0.2409</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3537</v>
+        <v>2.7845</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3059</v>
+        <v>-3.0253</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3061</v>
@@ -1078,13 +1078,13 @@
         <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0429</v>
+        <v>-0.3316</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1303</v>
+        <v>0.3005</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9126</v>
+        <v>-0.6321</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3736</v>
+        <v>-0.921</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8663</v>
+        <v>-0.4978</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5074</v>
+        <v>-0.4232</v>
       </c>
       <c r="G9" t="n">
         <v>0.2934</v>
@@ -1156,13 +1156,13 @@
         <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6751</v>
+        <v>-0.2225</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5611</v>
+        <v>-0.1927</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.114</v>
+        <v>-0.0298</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5232</v>
+        <v>-1.766</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.605</v>
+        <v>-0.0722</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9182</v>
+        <v>-1.6937</v>
       </c>
       <c r="G10" t="n">
         <v>0.0721</v>
@@ -1234,13 +1234,13 @@
         <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5079</v>
+        <v>0.2494</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0452</v>
+        <v>0.4876</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4626</v>
+        <v>-0.2382</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4842</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9138</v>
+        <v>-2.627</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3388</v>
+        <v>-3.2764</v>
       </c>
       <c r="F11" t="n">
-        <v>0.425</v>
+        <v>0.6495</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9071</v>
@@ -1312,13 +1312,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3821</v>
+        <v>0.6688</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5669</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1224</v>
+        <v>0.102</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.3523</v>
+        <v>18.28730000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>19.7793</v>
+        <v>20.7144</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4271</v>
+        <v>-2.427099999999999</v>
       </c>
       <c r="G12" t="n">
         <v>13.4413</v>
@@ -1390,13 +1390,13 @@
         <v>14.8788</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9271</v>
+        <v>2.8622</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7216</v>
+        <v>3.6568</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7944</v>
+        <v>-0.7945000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>4.440892098500626e-16</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MARTIN MONZON</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3155</v>
+        <v>1.0564</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5891</v>
+        <v>3.4414</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2736</v>
+        <v>-2.3851</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6902</v>
+        <v>-1.4572</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5344</v>
+        <v>-0.6604</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1557</v>
+        <v>-0.7967</v>
       </c>
       <c r="J13" t="n">
-        <v>0.218</v>
+        <v>2.3264</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5476</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7655999999999999</v>
+        <v>1.3279</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.9082</v>
+        <v>-3.7836</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9868</v>
+        <v>-1.659</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.9213</v>
+        <v>-2.1246</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9037</v>
+        <v>-0.4945</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1323</v>
+        <v>-0.306</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2286</v>
+        <v>-0.1885</v>
       </c>
       <c r="V13" t="n">
-        <v>4.102</v>
+        <v>2.4129</v>
       </c>
       <c r="W13" t="n">
-        <v>4.2226</v>
+        <v>2.4129</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0213</v>
+        <v>0.9295</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0508</v>
+        <v>-0.1532</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9705</v>
+        <v>1.0827</v>
       </c>
       <c r="G14" t="n">
         <v>0.6635</v>
@@ -1546,13 +1546,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3696</v>
+        <v>0.2778</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1531</v>
+        <v>-0.0509</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2165</v>
+        <v>0.3287</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4085</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>J. MARTIN MONZON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0438</v>
+        <v>0.2181</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6252</v>
+        <v>3.5282</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5814</v>
+        <v>-3.3101</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4572</v>
+        <v>-4.6902</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6604</v>
+        <v>-2.5344</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7967</v>
+        <v>-2.1557</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3264</v>
+        <v>0.218</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9985000000000001</v>
+        <v>-0.5476</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3279</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7836</v>
+        <v>-4.9082</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.659</v>
+        <v>-1.9868</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1246</v>
+        <v>-2.9213</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5071</v>
+        <v>0.8063</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1222</v>
+        <v>1.0714</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3849</v>
+        <v>-0.2651</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4129</v>
+        <v>4.102</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4129</v>
+        <v>4.2226</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7267</v>
+        <v>-0.0108</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1408</v>
+        <v>2.753</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8676</v>
+        <v>-2.7638</v>
       </c>
       <c r="G16" t="n">
         <v>1.7224</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.0255</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6008</v>
+        <v>0.0114</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1407</v>
+        <v>-0.0369</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1206</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9591</v>
+        <v>-0.5594</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5837</v>
+        <v>0.9919</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5428</v>
+        <v>-1.5513</v>
       </c>
       <c r="G17" t="n">
         <v>1.9353</v>
@@ -1780,13 +1780,13 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0793</v>
+        <v>0.4789</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.289</v>
+        <v>0.1191</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3683</v>
+        <v>0.3598</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9899</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MEDORI MORALES</t>
+          <t>P. GUASCH BENLLOCH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0946</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9859</v>
+        <v>-0.007</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0805</v>
+        <v>-0.9915</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8504</v>
+        <v>-0.2256</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2621</v>
+        <v>-0.0002</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5883</v>
+        <v>-0.2254</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3858</v>
+        <v>0.1006</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9312</v>
+        <v>0.0605</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4545</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2362</v>
+        <v>-0.3263</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1933</v>
+        <v>-0.0607</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0428</v>
+        <v>-0.2656</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.1615</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5839</v>
+        <v>-0.1077</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5091</v>
+        <v>-0.0539</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1206</v>
+        <v>-1.2065</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1206</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. GUASCH BENLLOCH</t>
+          <t>J. MEDORI MORALES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1464</v>
+        <v>-1.1949</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2111</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9353</v>
+        <v>-1.9767</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2256</v>
+        <v>-0.8504</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0002</v>
+        <v>-0.2621</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2254</v>
+        <v>-0.5883</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1006</v>
+        <v>2.3858</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0605</v>
+        <v>1.9312</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>0.4545</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3263</v>
+        <v>-3.2362</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0607</v>
+        <v>-2.1933</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2656</v>
+        <v>-1.0428</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3095</v>
+        <v>-0.0255</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3117</v>
+        <v>0.3799</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0022</v>
+        <v>-0.4054</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2065</v>
+        <v>-0.1206</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6493</v>
+        <v>-1.4529</v>
       </c>
       <c r="E20" t="n">
         <v>-1.2653</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3839</v>
+        <v>-0.1876</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7535</v>
@@ -2014,13 +2014,13 @@
         <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4415</v>
+        <v>-0.2451</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0283</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4132</v>
+        <v>-0.2168</v>
       </c>
       <c r="V20" t="n">
         <v>-0.0494</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3641</v>
+        <v>-2.0759</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3959</v>
+        <v>0.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.76</v>
+        <v>-2.6758</v>
       </c>
       <c r="G21" t="n">
         <v>0.1174</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4653</v>
+        <v>-0.1771</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2494</v>
+        <v>-0.0453</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.216</v>
+        <v>-0.1318</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4129</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5055</v>
+        <v>-3.2107</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9701</v>
+        <v>-2.2559</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5354</v>
+        <v>-0.9547</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6793</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5684</v>
+        <v>-0.2735</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6744</v>
+        <v>0.0398</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8939</v>
+        <v>-0.3132</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.287000000000001</v>
+        <v>-8.6927</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.4979</v>
+        <v>-5.9878</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7891</v>
+        <v>-2.7049</v>
       </c>
       <c r="G23" t="n">
         <v>-7.2237</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3212</v>
+        <v>-0.7269</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7991</v>
+        <v>-0.289</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5221</v>
+        <v>-0.4379</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9405</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.3521</v>
+        <v>-15.9918</v>
       </c>
       <c r="E24" t="n">
-        <v>2.426999999999998</v>
+        <v>2.427099999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-19.7791</v>
+        <v>-18.4188</v>
       </c>
       <c r="G24" t="n">
         <v>-13.4413</v>
@@ -2326,16 +2326,16 @@
         <v>12.8951</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.927</v>
+        <v>-0.5666</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7944000000000001</v>
+        <v>0.7944000000000002</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.7215</v>
+        <v>-1.361</v>
       </c>
       <c r="V24" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>5.551115123125783e-16</v>
       </c>
       <c r="W24" t="n">
         <v>6.493</v>
